--- a/Project Outputs for UZ_D_Inverter/Rev03/BOM/BOM_UZ_D_Inverter_Variant_V1_Rev03_ZC.xlsx
+++ b/Project Outputs for UZ_D_Inverter/Rev03/BOM/BOM_UZ_D_Inverter_Variant_V1_Rev03_ZC.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ga92wum\git\UltraZohm\PCB\uz_d_inverter\Project Outputs for UZ_D_Inverter\Rev03\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\nas.ads.mwn.de\ga92wum\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40EE849-B00F-4C30-8650-E8A95E8DF879}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8364A513-5345-4A57-A645-F25676B3378E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="18600" windowHeight="9100" xr2:uid="{C1292180-2071-4134-BAF2-D6614F20D6EA}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="win-source order" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BOM_UZ_D_Inverter_Variant_V1_Re!$B$1:$R$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BOM_UZ_D_Inverter_Variant_V1_Re!$B$1:$S$26</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">BOM_UZ_D_Inverter_Variant_V1_Re!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="227">
   <si>
     <t>Quantity</t>
   </si>
@@ -708,6 +708,9 @@
   </si>
   <si>
     <t>C278544</t>
+  </si>
+  <si>
+    <t>Winsource costs total</t>
   </si>
 </sst>
 </file>
@@ -934,7 +937,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -996,6 +999,16 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Eingabe" xfId="5" builtinId="20"/>
@@ -1316,29 +1329,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30F0FAA2-4651-4E33-9387-2A8604478B25}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:W36"/>
+  <dimension ref="A1:X36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="9.26953125" customWidth="1"/>
     <col min="3" max="3" width="31" customWidth="1"/>
-    <col min="4" max="4" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="9" max="9" width="42.90625" customWidth="1"/>
-    <col min="10" max="10" width="31.453125" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="35.7265625" customWidth="1"/>
-    <col min="13" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="15.08984375" customWidth="1"/>
-    <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="9" customWidth="1"/>
-    <col min="18" max="18" width="7.54296875" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" customWidth="1"/>
+    <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="42.90625" customWidth="1"/>
+    <col min="11" max="11" width="31.453125" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="35.7265625" customWidth="1"/>
+    <col min="14" max="15" width="16" customWidth="1"/>
+    <col min="16" max="16" width="15.08984375" customWidth="1"/>
+    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="19" max="19" width="7.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>11</v>
       </c>
@@ -1348,53 +1362,56 @@
       <c r="C1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
@@ -1406,35 +1423,36 @@
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
-      <c r="I2" s="2" t="s">
+      <c r="F2" s="8"/>
+      <c r="J2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>27</v>
       </c>
@@ -1446,35 +1464,36 @@
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="I3" s="2" t="s">
+      <c r="F3" s="8"/>
+      <c r="J3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="M3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="Q3" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R3" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -1486,35 +1505,36 @@
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
-      <c r="I4" s="2" t="s">
+      <c r="F4" s="8"/>
+      <c r="J4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="Q4" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+      <c r="R4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>225</v>
       </c>
@@ -1524,57 +1544,58 @@
       <c r="C5" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="5">
+      <c r="D5" s="36"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="5">
         <f>B5*$C$30</f>
         <v>50</v>
       </c>
-      <c r="G5" s="22">
+      <c r="H5" s="22">
         <v>50</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="5"/>
+      <c r="J5" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="J5" s="31" t="s">
+      <c r="K5" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="N5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="P5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P5" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="Q5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="T5" t="s">
+      <c r="R5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U5" t="s">
         <v>189</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
         <v>190</v>
       </c>
-      <c r="V5" s="20" t="s">
+      <c r="W5" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="W5" s="21" t="s">
+      <c r="X5" s="21" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>44</v>
       </c>
@@ -1584,52 +1605,56 @@
       <c r="C6" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="37">
+        <f>E6*G6</f>
+        <v>12.5</v>
+      </c>
+      <c r="E6" s="15">
         <v>0.25</v>
       </c>
-      <c r="E6" s="17">
+      <c r="F6" s="17">
         <v>0.35</v>
       </c>
-      <c r="F6" s="5">
+      <c r="G6" s="5">
         <f>B6*$C$30</f>
         <v>50</v>
       </c>
-      <c r="G6" s="22">
+      <c r="H6" s="22">
         <v>150</v>
       </c>
-      <c r="H6" s="19">
-        <f>G6*D6</f>
+      <c r="I6" s="19">
+        <f>H6*E6</f>
         <v>37.5</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="N6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="Q6" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="R6" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>53</v>
       </c>
@@ -1641,35 +1666,36 @@
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
-      <c r="I7" s="2" t="s">
+      <c r="F7" s="8"/>
+      <c r="J7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="L7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>27</v>
       </c>
@@ -1681,35 +1707,36 @@
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
-      <c r="I8" s="2" t="s">
+      <c r="F8" s="8"/>
+      <c r="J8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="M8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="Q8" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="R8" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>185</v>
       </c>
@@ -1719,50 +1746,51 @@
       <c r="C9" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="15">
+      <c r="D9" s="36"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="15">
         <v>1.2</v>
       </c>
-      <c r="F9" s="5">
-        <f t="shared" ref="F9:F15" si="0">B9*$C$30</f>
+      <c r="G9" s="5">
+        <f t="shared" ref="G9:G15" si="0">B9*$C$30</f>
         <v>10</v>
       </c>
-      <c r="G9" s="22">
+      <c r="H9" s="22">
         <v>30</v>
       </c>
-      <c r="H9" s="19">
-        <f>G9*E9</f>
+      <c r="I9" s="19">
+        <f>H9*F9</f>
         <v>36</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="L9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="O9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="P9" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="Q9" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="R9" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>183</v>
       </c>
@@ -1772,50 +1800,51 @@
       <c r="C10" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="13">
+      <c r="D10" s="36"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="13">
         <v>1.52</v>
       </c>
-      <c r="F10" s="5">
+      <c r="G10" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G10" s="22">
+      <c r="H10" s="22">
         <v>15</v>
       </c>
-      <c r="H10" s="19">
-        <f>G10*E10</f>
+      <c r="I10" s="19">
+        <f>H10*F10</f>
         <v>22.8</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="N10" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="O10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="P10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="Q10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q10" s="2" t="s">
+      <c r="R10" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>1</v>
@@ -1823,50 +1852,51 @@
       <c r="C11" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="15">
+      <c r="D11" s="36"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="15">
         <v>7.78</v>
       </c>
-      <c r="F11" s="5">
+      <c r="G11" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G11" s="22">
+      <c r="H11" s="22">
         <v>10</v>
       </c>
-      <c r="H11" s="19">
-        <f>G11*E11</f>
+      <c r="I11" s="19">
+        <f>H11*F11</f>
         <v>77.8</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="N11" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="O11" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="P11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="P11" s="2" t="s">
+      <c r="Q11" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="R11" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>184</v>
       </c>
@@ -1876,50 +1906,51 @@
       <c r="C12" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="13">
+      <c r="D12" s="36"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="13">
         <v>1.52</v>
       </c>
-      <c r="F12" s="5">
+      <c r="G12" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="G12" s="22">
+      <c r="H12" s="22">
         <v>20</v>
       </c>
-      <c r="H12" s="19">
-        <f>G12*E12</f>
+      <c r="I12" s="19">
+        <f>H12*F12</f>
         <v>30.4</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="M12" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="N12" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="O12" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="O12" s="2" t="s">
+      <c r="P12" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="P12" s="2" t="s">
+      <c r="Q12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="R12" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" ht="58" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>95</v>
       </c>
@@ -1929,50 +1960,51 @@
       <c r="C13" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="13">
+      <c r="D13" s="36"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="13">
         <v>0.14000000000000001</v>
       </c>
-      <c r="F13" s="5">
+      <c r="G13" s="5">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
-      <c r="G13" s="22">
+      <c r="H13" s="22">
         <v>150</v>
       </c>
-      <c r="H13" s="19">
-        <f>G13*E13</f>
+      <c r="I13" s="19">
+        <f>H13*F13</f>
         <v>21.000000000000004</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="J13" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="L13" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="M13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="N13" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="O13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="P13" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="P13" s="2" t="s">
+      <c r="Q13" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="Q13" s="2" t="s">
+      <c r="R13" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>103</v>
       </c>
@@ -1982,47 +2014,48 @@
       <c r="C14" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="13">
+      <c r="D14" s="36"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="13">
         <v>4.8</v>
       </c>
-      <c r="F14" s="5">
+      <c r="G14" s="5">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="G14" s="22">
+      <c r="H14" s="22">
         <v>30</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="5"/>
+      <c r="J14" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="L14" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="M14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="N14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="O14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O14" s="2" t="s">
+      <c r="P14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="P14" s="2" t="s">
+      <c r="Q14" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="Q14" s="2" t="s">
+      <c r="R14" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>27</v>
       </c>
@@ -2032,53 +2065,57 @@
       <c r="C15" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="37">
+        <f>E15*G15</f>
+        <v>37.200000000000003</v>
+      </c>
+      <c r="E15" s="15">
         <v>1.24</v>
       </c>
-      <c r="E15" s="12">
+      <c r="F15" s="12">
         <v>1.55</v>
       </c>
-      <c r="F15" s="5">
+      <c r="G15" s="5">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="G15" s="22">
+      <c r="H15" s="22">
         <f>'win-source order'!C4</f>
         <v>100</v>
       </c>
-      <c r="H15" s="19">
-        <f>G15*D15</f>
+      <c r="I15" s="19">
+        <f>H15*E15</f>
         <v>124</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="L15" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="M15" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="N15" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="O15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="P15" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="P15" s="2" t="s">
+      <c r="Q15" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="Q15" s="2" t="s">
+      <c r="R15" s="2" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>119</v>
       </c>
@@ -2088,39 +2125,40 @@
       <c r="C16" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="8"/>
+      <c r="E16" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="I16" s="2" t="s">
+      <c r="F16" s="8"/>
+      <c r="J16" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="L16" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="M16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="N16" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="O16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="P16" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="Q16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="Q16" s="2" t="s">
+      <c r="R16" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>126</v>
       </c>
@@ -2130,37 +2168,54 @@
       <c r="C17" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="I17" s="2" t="s">
+      <c r="D17" s="37">
+        <f>E17*G17</f>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0.41</v>
+      </c>
+      <c r="F17" s="8"/>
+      <c r="G17" s="5">
+        <f t="shared" ref="G17" si="1">B17*$C$30</f>
+        <v>20</v>
+      </c>
+      <c r="H17" s="22">
+        <v>100</v>
+      </c>
+      <c r="I17" s="19">
+        <f>H17*E17</f>
+        <v>41</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="K17" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="L17" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="M17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="N17" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="O17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O17" s="2" t="s">
+      <c r="P17" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="P17" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="Q17" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R17" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>133</v>
       </c>
@@ -2172,35 +2227,36 @@
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="I18" s="2" t="s">
+      <c r="F18" s="8"/>
+      <c r="J18" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="K18" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="L18" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="M18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="N18" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="O18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O18" s="2" t="s">
+      <c r="P18" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="P18" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="Q18" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R18" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>27</v>
       </c>
@@ -2212,35 +2268,36 @@
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
-      <c r="I19" s="2" t="s">
+      <c r="F19" s="8"/>
+      <c r="J19" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="K19" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="L19" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="M19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="N19" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="O19" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O19" s="2" t="s">
+      <c r="P19" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="P19" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="Q19" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="R19" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
@@ -2252,35 +2309,36 @@
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
-      <c r="I20" s="2" t="s">
+      <c r="F20" s="8"/>
+      <c r="J20" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="K20" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="L20" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="L20" s="2" t="s">
+      <c r="M20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="N20" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>142</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="Q20" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R20" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>149</v>
       </c>
@@ -2290,50 +2348,54 @@
       <c r="C21" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="37">
+        <f t="shared" ref="D21:D22" si="2">E21*G21</f>
+        <v>83.2</v>
+      </c>
+      <c r="E21" s="15">
         <v>4.16</v>
       </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="5">
-        <f t="shared" ref="F21:F26" si="1">B21*$C$30</f>
+      <c r="F21" s="8"/>
+      <c r="G21" s="5">
+        <f t="shared" ref="G21:G26" si="3">B21*$C$30</f>
         <v>20</v>
       </c>
-      <c r="G21" s="22">
+      <c r="H21" s="22">
         <v>20</v>
       </c>
-      <c r="H21" s="19">
-        <f>G21*D21</f>
+      <c r="I21" s="19">
+        <f>H21*E21</f>
         <v>83.2</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="J21" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="K21" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="K21" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="L21" s="2" t="s">
         <v>27</v>
       </c>
       <c r="M21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="O21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O21" s="2" t="s">
+      <c r="P21" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="P21" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="Q21" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+      <c r="R21" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>156</v>
       </c>
@@ -2343,53 +2405,57 @@
       <c r="C22" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="37">
+        <f t="shared" si="2"/>
+        <v>81.199999999999989</v>
+      </c>
+      <c r="E22" s="15">
         <v>2.0299999999999998</v>
       </c>
-      <c r="E22" s="18">
+      <c r="F22" s="18">
         <v>3.25</v>
       </c>
-      <c r="F22" s="5">
-        <f t="shared" si="1"/>
+      <c r="G22" s="5">
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="G22" s="22">
+      <c r="H22" s="22">
         <f>'win-source order'!C6</f>
         <v>120</v>
       </c>
-      <c r="H22" s="19">
-        <f>G22*D22</f>
+      <c r="I22" s="19">
+        <f>H22*E22</f>
         <v>243.59999999999997</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="J22" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="K22" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="K22" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="L22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M22" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="N22" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="O22" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O22" s="2" t="s">
+      <c r="P22" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="P22" s="2" t="s">
+      <c r="Q22" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="Q22" s="2" t="s">
+      <c r="R22" s="2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>163</v>
       </c>
@@ -2399,49 +2465,50 @@
       <c r="C23" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="E23" s="15">
+      <c r="D23" s="36"/>
+      <c r="F23" s="15">
         <v>1.4</v>
       </c>
-      <c r="F23" s="5">
-        <f t="shared" si="1"/>
+      <c r="G23" s="5">
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="G23" s="22">
+      <c r="H23" s="22">
         <v>30</v>
       </c>
-      <c r="H23" s="19">
-        <f>G23*E23</f>
+      <c r="I23" s="19">
+        <f>H23*F23</f>
         <v>42</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="J23" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="J23" s="31" t="s">
+      <c r="K23" s="31" t="s">
         <v>222</v>
       </c>
-      <c r="K23" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="L23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="N23" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="O23" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O23" s="2" t="s">
+      <c r="P23" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="P23" s="2" t="s">
+      <c r="Q23" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="Q23" s="2" t="s">
+      <c r="R23" s="2" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>168</v>
       </c>
@@ -2451,50 +2518,54 @@
       <c r="C24" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="37">
+        <f t="shared" ref="D24:D25" si="4">E24*G24</f>
+        <v>118.5</v>
+      </c>
+      <c r="E24" s="15">
         <v>3.95</v>
       </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="5">
+      <c r="F24" s="8"/>
+      <c r="G24" s="5">
         <f>B24*$C$30</f>
         <v>30</v>
       </c>
-      <c r="G24" s="22">
+      <c r="H24" s="22">
         <v>30</v>
       </c>
-      <c r="H24" s="19">
-        <f>G24*D24</f>
+      <c r="I24" s="19">
+        <f>H24*E24</f>
         <v>118.5</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="J24" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="J24" s="31" t="s">
+      <c r="K24" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="K24" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="L24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="N24" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="O24" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="P24" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="P24" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="Q24" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R24" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>27</v>
       </c>
@@ -2504,51 +2575,55 @@
       <c r="C25" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="37">
+        <f t="shared" si="4"/>
+        <v>15.450000000000001</v>
+      </c>
+      <c r="E25" s="15">
         <v>1.03</v>
       </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="5">
-        <f t="shared" si="1"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="5">
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="G25" s="22">
+      <c r="H25" s="22">
         <f>'win-source order'!C9</f>
         <v>50</v>
       </c>
-      <c r="H25" s="19">
-        <f>G25*D25</f>
+      <c r="I25" s="19">
+        <f>H25*E25</f>
         <v>51.5</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="J25" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="K25" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="K25" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="L25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="N25" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="O25" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O25" s="2" t="s">
+      <c r="P25" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="P25" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="Q25" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R25" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>178</v>
       </c>
@@ -2558,78 +2633,87 @@
       <c r="C26" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="15">
+      <c r="D26" s="36"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="15">
         <v>0.13</v>
       </c>
-      <c r="F26" s="5">
-        <f t="shared" si="1"/>
+      <c r="G26" s="5">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="G26" s="22">
+      <c r="H26" s="22">
         <v>50</v>
       </c>
-      <c r="H26" s="19">
-        <f>G26*E26</f>
+      <c r="I26" s="19">
+        <f>H26*F26</f>
         <v>6.5</v>
       </c>
-      <c r="I26" s="2" t="s">
+      <c r="J26" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="K26" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="K26" s="1"/>
-      <c r="L26" s="2" t="s">
+      <c r="L26" s="1"/>
+      <c r="M26" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="N26" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="N26" s="2" t="s">
+      <c r="O26" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O26" s="2" t="s">
+      <c r="P26" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R26" s="1"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="C27" s="11"/>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="D27" s="11"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
       <c r="C28" s="11"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="D28" s="11"/>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
       <c r="C29" s="11"/>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="D29" s="11"/>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B30" s="5" t="s">
         <v>180</v>
       </c>
       <c r="C30" s="5">
         <v>5</v>
       </c>
-      <c r="H30" s="19">
-        <f>SUM(H5:H29)</f>
-        <v>894.8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="D32" s="16"/>
-    </row>
-    <row r="33" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="F33">
+      <c r="D30" s="5">
+        <f>SUM(D5:D29)</f>
+        <v>356.25</v>
+      </c>
+      <c r="I30" s="19">
+        <f>SUM(I5:I29)</f>
+        <v>935.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="E32" s="16"/>
+    </row>
+    <row r="33" spans="3:7" x14ac:dyDescent="0.35">
+      <c r="G33">
         <f>125*3</f>
         <v>375</v>
       </c>
     </row>
-    <row r="36" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:R26" xr:uid="{EF2E5A5C-2B03-424E-BA44-AFB38E8D7EB7}">
+  <autoFilter ref="B1:S26" xr:uid="{EF2E5A5C-2B03-424E-BA44-AFB38E8D7EB7}">
     <filterColumn colId="1">
       <filters>
         <filter val="C40, C41, C42, C43, C44, C45, C46, C47, C48, C49"/>
@@ -2643,6 +2727,7 @@
         <filter val="L1A, L1B, L1C, L2A, L2B, L2C, L3A, L3B, L3C, L4A, L4B, L4C, L5A, L5B, L5C, L6, L7, L8, L9A, L9B, L9C, L10A, L10B, L10C, L12"/>
         <filter val="PS1A, PS1B, PS1C, PS2A, PS2B, PS2C"/>
         <filter val="Q1A, Q1B, Q1C, Q2A, Q2B, Q2C"/>
+        <filter val="R10A, R10B, R10C, R50"/>
         <filter val="U13"/>
         <filter val="U2A, U2B, U2C, U11"/>
         <filter val="U3A, U3B, U3C, U4A, U4B, U4C, U10, U12"/>
@@ -2653,7 +2738,7 @@
     </filterColumn>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="V5" r:id="rId1" display="https://www.lcsc.com/product-detail/Aluminum-Electrolytic-Capacitors-SMD_Vishay-Intertech-MAL215099907E3_C1984845.html" xr:uid="{452CC0EA-8F1F-4817-975B-A4F9D03D6520}"/>
+    <hyperlink ref="W5" r:id="rId1" display="https://www.lcsc.com/product-detail/Aluminum-Electrolytic-Capacitors-SMD_Vishay-Intertech-MAL215099907E3_C1984845.html" xr:uid="{452CC0EA-8F1F-4817-975B-A4F9D03D6520}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -2662,7 +2747,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E336E9DB-6A9A-4A8B-AA62-AD8D1B249CBB}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
@@ -2898,8 +2983,19 @@
         <v>218</v>
       </c>
     </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="38">
+        <v>100</v>
+      </c>
+    </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="F11" s="29">
+      <c r="A11" s="38"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="38"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F13" s="29">
         <f>SUM(F3:F10)</f>
         <v>665.83999999999992</v>
       </c>
